--- a/public/templates/Inspection_checklist_template.xlsx
+++ b/public/templates/Inspection_checklist_template.xlsx
@@ -53,7 +53,7 @@
     <t>Enter the name of the checklist</t>
   </si>
   <si>
-    <t>Enter the name of the description</t>
+    <t>Enter the description of the checklist</t>
   </si>
   <si>
     <t>Enter the detail name of the checklist</t>
